--- a/ExcelProject/Deposit_Money.xlsx
+++ b/ExcelProject/Deposit_Money.xlsx
@@ -1,57 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DepositMoney" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="DepositMoney"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+  <si>
+    <t>Execute</t>
+  </si>
+  <si>
+    <t>TestCase</t>
+  </si>
+  <si>
+    <t>deposit</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Revise</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>TC7:01</t>
+  </si>
+  <si>
+    <t>เติมเงินสำเร็จ</t>
+  </si>
+  <si>
+    <t>TC7:02</t>
+  </si>
+  <si>
+    <t>กรุณากรอกเป็นตัวเลขจำนวนเต็มเป็นเงินบาท</t>
+  </si>
+  <si>
+    <t>TC7:03</t>
+  </si>
+  <si>
+    <t>TC7:04</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>TC7:05</t>
+  </si>
+  <si>
+    <t>ยอดเงินขั้นต่ำ 100 บาท</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TC7:06</t>
+  </si>
+  <si>
+    <t>กรุณากรอกจำนวนเงิน</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Angsana New"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Angsana New"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="16"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -99,128 +158,63 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="15">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -508,244 +502,191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="9.147857142857141" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="13.005" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
-    <col width="9.147857142857141" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="27.86214285714286" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
-    <col width="20.14785714285714" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="13" min="6" max="6"/>
-    <col width="26.57642857142857" bestFit="1" customWidth="1" style="13" min="7" max="7"/>
+    <col min="1" max="1" style="13" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="27.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="26.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Execute</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Revise</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>TC7:01</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5">
         <v>1000</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>เติมเงินสำเร็จ</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>TC7:02</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5">
         <v>100.5</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>กรุณากรอกเป็นตัวเลขจำนวนเต็มเป็นเงินบาท</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>TC7:03</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5">
         <v>100</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>เติมเงินสำเร็จ</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>TC7:04</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5">
         <v>101</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>เติมเงินสำเร็จ</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="21.75" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>TC7:05</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5">
         <v>99</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ยอดเงินขั้นต่ำ 100 บาท</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>TC7:06</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>กรุณากรอกจำนวนเงิน</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="21.75" customHeight="1">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
+      <c r="A9" s="11"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
+      <c r="A10" s="11"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
+      <c r="A11" s="11"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
+      <c r="A12" s="11"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelProject/Deposit_Money.xlsx
+++ b/ExcelProject/Deposit_Money.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
   <si>
     <t>Execute</t>
   </si>
@@ -46,28 +46,40 @@
     <t>เติมเงินสำเร็จ</t>
   </si>
   <si>
+    <t>เงินฝากสำเร็จแล้ว จำนวน: 101 บาท กด OK เพื่อกลับหน้า Home</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>TC7:02</t>
   </si>
   <si>
     <t>กรุณากรอกเป็นตัวเลขจำนวนเต็มเป็นเงินบาท</t>
   </si>
   <si>
+    <t>เงินฝากสำเร็จแล้ว จำนวน: 1000 บาท กด OK เพื่อกลับหน้า Home</t>
+  </si>
+  <si>
     <t>TC7:03</t>
   </si>
   <si>
     <t>TC7:04</t>
   </si>
   <si>
+    <t>เงินฝากสำเร็จแล้ว จำนวน: 100 บาท กด OK เพื่อกลับหน้า Home</t>
+  </si>
+  <si>
+    <t>TC7:05</t>
+  </si>
+  <si>
+    <t>จำนวนเงินขั้นต่ำคือ 100 บาท</t>
+  </si>
+  <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>TC7:05</t>
-  </si>
-  <si>
-    <t>ยอดเงินขั้นต่ำ 100 บาท</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>TC7:06</t>
@@ -80,7 +92,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -160,12 +174,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -174,34 +188,25 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -509,13 +514,13 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="27.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="20.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="26.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="27.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="41.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="26.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27">
@@ -541,7 +546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -554,33 +559,45 @@
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6">
         <v>100.5</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" s="5">
         <v>100</v>
@@ -588,16 +605,22 @@
       <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5">
         <v>101</v>
@@ -605,88 +628,104 @@
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5">
         <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
-      <c r="A9" s="11"/>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
+      <c r="A9" s="9"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
-      <c r="A10" s="11"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
+      <c r="A10" s="9"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
-      <c r="A11" s="11"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
+      <c r="A11" s="9"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
-      <c r="A12" s="11"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
+      <c r="A12" s="9"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelProject/Deposit_Money.xlsx
+++ b/ExcelProject/Deposit_Money.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>Execute</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Revise</t>
   </si>
   <si>
-    <t>N</t>
+    <t>Y</t>
   </si>
   <si>
     <t>TC7:01</t>
@@ -46,40 +46,37 @@
     <t>เติมเงินสำเร็จ</t>
   </si>
   <si>
-    <t>เงินฝากสำเร็จแล้ว จำนวน: 101 บาท กด OK เพื่อกลับหน้า Home</t>
+    <t>เงินฝากสำเร็จแล้ว จำนวน: 500 บาท กด OK เพื่อกลับหน้า Home</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
+    <t>TC7:02</t>
+  </si>
+  <si>
+    <t>กรุณากรอกเป็นตัวเลขจำนวนเต็มเป็นเงินบาท</t>
+  </si>
+  <si>
+    <t>เงินฝากสำเร็จแล้ว จำนวน: 1000 บาท กด OK เพื่อกลับหน้า Home</t>
+  </si>
+  <si>
+    <t>TC7:03</t>
+  </si>
+  <si>
+    <t>TC7:04</t>
+  </si>
+  <si>
+    <t>เงินฝากสำเร็จแล้ว จำนวน: 100 บาท กด OK เพื่อกลับหน้า Home</t>
+  </si>
+  <si>
+    <t>TC7:05</t>
+  </si>
+  <si>
+    <t>จำนวนเงินขั้นต่ำคือ 100 บาท</t>
+  </si>
+  <si>
     <t>Pass</t>
-  </si>
-  <si>
-    <t>TC7:02</t>
-  </si>
-  <si>
-    <t>กรุณากรอกเป็นตัวเลขจำนวนเต็มเป็นเงินบาท</t>
-  </si>
-  <si>
-    <t>เงินฝากสำเร็จแล้ว จำนวน: 1000 บาท กด OK เพื่อกลับหน้า Home</t>
-  </si>
-  <si>
-    <t>TC7:03</t>
-  </si>
-  <si>
-    <t>TC7:04</t>
-  </si>
-  <si>
-    <t>เงินฝากสำเร็จแล้ว จำนวน: 100 บาท กด OK เพื่อกลับหน้า Home</t>
-  </si>
-  <si>
-    <t>TC7:05</t>
-  </si>
-  <si>
-    <t>จำนวนเงินขั้นต่ำคือ 100 บาท</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>TC7:06</t>
@@ -523,7 +520,7 @@
     <col min="7" max="7" style="10" width="26.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
@@ -574,16 +571,16 @@
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="6">
         <v>100.5</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>11</v>
@@ -597,7 +594,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="5">
         <v>100</v>
@@ -606,13 +603,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
@@ -620,7 +617,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="5">
         <v>101</v>
@@ -629,13 +626,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
@@ -643,43 +640,43 @@
         <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5">
         <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">

--- a/ExcelProject/Deposit_Money.xlsx
+++ b/ExcelProject/Deposit_Money.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Test-Tutor-main\ExcelProject\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF8BA9F-B0B6-4790-98D9-FA7D364F06CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12960" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="DepositMoney"/>
+    <sheet name="DepositMoney" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -55,9 +61,6 @@
     <t>TC7:02</t>
   </si>
   <si>
-    <t>กรุณากรอกเป็นตัวเลขจำนวนเต็มเป็นเงินบาท</t>
-  </si>
-  <si>
     <t>เงินฝากสำเร็จแล้ว จำนวน: 1000 บาท กด OK เพื่อกลับหน้า Home</t>
   </si>
   <si>
@@ -83,12 +86,15 @@
   </si>
   <si>
     <t>กรุณากรอกจำนวนเงิน</t>
+  </si>
+  <si>
+    <t>จำนวนต้องเป็นตัวเลขจำนวนเต็ม</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
@@ -128,12 +134,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFd9d9d9"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFdeebf7"/>
+        <fgColor rgb="FFDEEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,49 +178,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -225,10 +234,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -266,71 +275,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -358,7 +367,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -381,11 +390,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -394,13 +403,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -410,7 +419,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -419,7 +428,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -428,7 +437,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -436,10 +445,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -504,23 +513,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="27.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="41.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="26.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="9.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27.75">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,7 +552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21">
+    <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -566,7 +575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
+    <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -577,24 +586,24 @@
         <v>100.5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5">
         <v>100</v>
@@ -603,7 +612,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>11</v>
@@ -612,12 +621,12 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
+    <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5">
         <v>101</v>
@@ -626,7 +635,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>11</v>
@@ -635,51 +644,51 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
+    <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="5">
         <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
+    </row>
+    <row r="7" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -688,7 +697,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
+    <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
@@ -697,7 +706,7 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
+    <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
@@ -706,7 +715,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
+    <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
@@ -715,7 +724,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
+    <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
